--- a/data/trans_orig/P20D1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -991,62 +991,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1221,62 +1221,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2657</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6608</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>34,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2657</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6557</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -1334,62 +1334,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>30,54%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>6721</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>30,54%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -1412,97 +1412,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7710</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2698</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2698</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2698</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6289</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>34,99%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,48%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12425</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>315</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>423</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>46552</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>65881</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>45380</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Edad-trans_orig.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>380</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>516</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>333</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>348</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>65833</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65881</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45380</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
